--- a/artfynd/A 41404-2023 artfynd.xlsx
+++ b/artfynd/A 41404-2023 artfynd.xlsx
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455557</v>
+        <v>117455555</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486281</v>
+        <v>486661</v>
       </c>
       <c r="R4" t="n">
-        <v>7085738</v>
+        <v>7085696</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117455570</v>
+        <v>117455565</v>
       </c>
       <c r="B5" t="n">
         <v>57287</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486605</v>
+        <v>486673</v>
       </c>
       <c r="R5" t="n">
-        <v>7085921</v>
+        <v>7085800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117455565</v>
+        <v>117455568</v>
       </c>
       <c r="B6" t="n">
         <v>57287</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486673</v>
+        <v>486628</v>
       </c>
       <c r="R6" t="n">
-        <v>7085800</v>
+        <v>7085938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117455572</v>
+        <v>117455570</v>
       </c>
       <c r="B7" t="n">
         <v>57287</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486596</v>
+        <v>486605</v>
       </c>
       <c r="R7" t="n">
-        <v>7085890</v>
+        <v>7085921</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117455579</v>
+        <v>117455580</v>
       </c>
       <c r="B8" t="n">
         <v>57287</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486379</v>
+        <v>486475</v>
       </c>
       <c r="R8" t="n">
-        <v>7086071</v>
+        <v>7086010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117455575</v>
+        <v>117455582</v>
       </c>
       <c r="B9" t="n">
         <v>57287</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486581</v>
+        <v>486741</v>
       </c>
       <c r="R9" t="n">
-        <v>7085945</v>
+        <v>7085958</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117455582</v>
+        <v>117455573</v>
       </c>
       <c r="B10" t="n">
         <v>57287</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486741</v>
+        <v>486591</v>
       </c>
       <c r="R10" t="n">
-        <v>7085958</v>
+        <v>7085928</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117455577</v>
+        <v>117455556</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486589</v>
+        <v>486592</v>
       </c>
       <c r="R11" t="n">
-        <v>7085945</v>
+        <v>7085660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117455568</v>
+        <v>117455575</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>486628</v>
+        <v>486581</v>
       </c>
       <c r="R12" t="n">
-        <v>7085938</v>
+        <v>7085945</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117455567</v>
+        <v>117455577</v>
       </c>
       <c r="B13" t="n">
         <v>57287</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486661</v>
+        <v>486589</v>
       </c>
       <c r="R13" t="n">
-        <v>7085940</v>
+        <v>7085945</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117455573</v>
+        <v>117455579</v>
       </c>
       <c r="B14" t="n">
         <v>57287</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486591</v>
+        <v>486379</v>
       </c>
       <c r="R14" t="n">
-        <v>7085928</v>
+        <v>7086071</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117455555</v>
+        <v>117455572</v>
       </c>
       <c r="B15" t="n">
         <v>57287</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486661</v>
+        <v>486596</v>
       </c>
       <c r="R15" t="n">
-        <v>7085696</v>
+        <v>7085890</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117455556</v>
+        <v>117455557</v>
       </c>
       <c r="B16" t="n">
         <v>57287</v>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486592</v>
+        <v>486281</v>
       </c>
       <c r="R16" t="n">
-        <v>7085660</v>
+        <v>7085738</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117455580</v>
+        <v>117455558</v>
       </c>
       <c r="B17" t="n">
         <v>57287</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486475</v>
+        <v>486283</v>
       </c>
       <c r="R17" t="n">
-        <v>7086010</v>
+        <v>7085738</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117455558</v>
+        <v>117455567</v>
       </c>
       <c r="B18" t="n">
         <v>57287</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486283</v>
+        <v>486661</v>
       </c>
       <c r="R18" t="n">
-        <v>7085738</v>
+        <v>7085940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 41404-2023 artfynd.xlsx
+++ b/artfynd/A 41404-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117455595</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79563</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>117455600</v>
       </c>
       <c r="B3" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455555</v>
+        <v>117455568</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>486661</v>
+        <v>486628</v>
       </c>
       <c r="R4" t="n">
-        <v>7085696</v>
+        <v>7085938</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117455565</v>
+        <v>117455555</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>486673</v>
+        <v>486661</v>
       </c>
       <c r="R5" t="n">
-        <v>7085800</v>
+        <v>7085696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117455568</v>
+        <v>117455558</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>486628</v>
+        <v>486283</v>
       </c>
       <c r="R6" t="n">
-        <v>7085938</v>
+        <v>7085738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117455570</v>
+        <v>117455557</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>486605</v>
+        <v>486281</v>
       </c>
       <c r="R7" t="n">
-        <v>7085921</v>
+        <v>7085738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117455580</v>
+        <v>117455582</v>
       </c>
       <c r="B8" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>486475</v>
+        <v>486741</v>
       </c>
       <c r="R8" t="n">
-        <v>7086010</v>
+        <v>7085958</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117455582</v>
+        <v>117455580</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>486741</v>
+        <v>486475</v>
       </c>
       <c r="R9" t="n">
-        <v>7085958</v>
+        <v>7086010</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117455573</v>
+        <v>117455572</v>
       </c>
       <c r="B10" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>486591</v>
+        <v>486596</v>
       </c>
       <c r="R10" t="n">
-        <v>7085928</v>
+        <v>7085890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117455556</v>
+        <v>117455570</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>486592</v>
+        <v>486605</v>
       </c>
       <c r="R11" t="n">
-        <v>7085660</v>
+        <v>7085921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,7 +1738,7 @@
         <v>117455575</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117455577</v>
+        <v>117455556</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>486589</v>
+        <v>486592</v>
       </c>
       <c r="R13" t="n">
-        <v>7085945</v>
+        <v>7085660</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117455579</v>
+        <v>117455577</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>486379</v>
+        <v>486589</v>
       </c>
       <c r="R14" t="n">
-        <v>7086071</v>
+        <v>7085945</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117455572</v>
+        <v>117455573</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>486596</v>
+        <v>486591</v>
       </c>
       <c r="R15" t="n">
-        <v>7085890</v>
+        <v>7085928</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117455557</v>
+        <v>117455567</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>486281</v>
+        <v>486661</v>
       </c>
       <c r="R16" t="n">
-        <v>7085738</v>
+        <v>7085940</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117455558</v>
+        <v>117455565</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>486283</v>
+        <v>486673</v>
       </c>
       <c r="R17" t="n">
-        <v>7085738</v>
+        <v>7085800</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117455567</v>
+        <v>117455579</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>486661</v>
+        <v>486379</v>
       </c>
       <c r="R18" t="n">
-        <v>7085940</v>
+        <v>7086071</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
